--- a/output/audits/resources_finance_audit.xlsx
+++ b/output/audits/resources_finance_audit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christopherwenz/Code/peer_schools/output/audits/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7EF680-05EC-B740-8E63-F84601BF5740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7BF39EB-EFB1-E04E-A47F-21D8B331206F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="27000" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resources + Finance" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="97">
   <si>
     <t>Theme</t>
   </si>
@@ -40,6 +40,12 @@
     <t>Format</t>
   </si>
   <si>
+    <t>Use type</t>
+  </si>
+  <si>
+    <t>Coverage note</t>
+  </si>
+  <si>
     <t>Definition (plain English)</t>
   </si>
   <si>
@@ -64,9 +70,18 @@
     <t>ratio</t>
   </si>
   <si>
+    <t>clustering</t>
+  </si>
+  <si>
+    <t>Computed (STUFACR not in IPEDS); matches NSC's published S-F ratio formula</t>
+  </si>
+  <si>
     <t>Number of full-time-equivalent students divided by full-time-equivalent instructional faculty. Lower numbers usually signal smaller classes. IPEDS doesn't publish STUFACR directly so this is computed from FTE enrollment and full-time-equivalent instructional staff. Matches the NSC and US News published versions for most institutions.</t>
   </si>
   <si>
+    <t>Keep: No high-correlation pair within Resources or across themes.</t>
+  </si>
+  <si>
     <t>tenure_track_share</t>
   </si>
   <si>
@@ -79,9 +94,15 @@
     <t>percentage</t>
   </si>
   <si>
+    <t>NA if institution has no tenure system (FACSTAT 40 populated, 20+30 empty)</t>
+  </si>
+  <si>
     <t>Percent of full-time instructional staff who are tenured or on the tenure track (FACSTAT 20 + 30 over FACSTAT 0 total). Higher values usually signal more stable, research-active faculty cores. NA for institutions without a tenure system at all (typically community colleges and some specialty schools). Source: IPEDS HR.</t>
   </si>
   <si>
+    <t>Keep: distinct signal (% of instructional staff tenured/tenure-track). No correlation issues.</t>
+  </si>
+  <si>
     <t>avg_ft_faculty_salary</t>
   </si>
   <si>
@@ -97,6 +118,9 @@
     <t>Average salary of full-time instructional faculty on 9-month contracts (equated where needed for 12-month contracts). Reflects compensation levels and, by proxy, hiring competitiveness. Source: IPEDS Human Resources (SAL).</t>
   </si>
   <si>
+    <t>Keep: faculty-investment signal that's distinct from expenses-per-FTE.</t>
+  </si>
+  <si>
     <t>instruction_per_fte</t>
   </si>
   <si>
@@ -112,6 +136,9 @@
     <t>Instruction expenses (faculty salaries, departmental support, instructional supplies) per FTE enrollment. The most direct per-student measure of spending on actual teaching. Source: IPEDS F.</t>
   </si>
   <si>
+    <t>Keep? But r = 0.871 with core_expenses_per_fte (Finance). Cross-theme overlap is defensible. Drop only if consolidating finance and resources into one theme?</t>
+  </si>
+  <si>
     <t>academic_support_per_fte</t>
   </si>
   <si>
@@ -124,6 +151,9 @@
     <t>Academic support expenses (libraries, academic computing, academic administration, etc.) divided by FTE enrollment. A measure of investment in the academic infrastructure surrounding direct instruction. Source: IPEDS F.</t>
   </si>
   <si>
+    <t>Keep: distinct line item (libraries, IT support, academic administration).</t>
+  </si>
+  <si>
     <t>student_services_per_fte</t>
   </si>
   <si>
@@ -136,6 +166,9 @@
     <t>Student services expenses (admissions, registrar, financial aid, career services, student health, student activities, etc.) per FTE enrollment. Captures non-academic-but-essential investment per student. Source: IPEDS F.</t>
   </si>
   <si>
+    <t>Keep: distinct line item (advising, registrar, student-life support).</t>
+  </si>
+  <si>
     <t>instructional_share</t>
   </si>
   <si>
@@ -148,28 +181,7 @@
     <t>Instruction as a percent of total core operating expenses. Tracks how much of operating spend goes to direct teaching costs (faculty, departments) vs. research, public service, support, etc. Most LACs run 35–50%; research universities are lower because more spending flows to research. Source: IPEDS F.</t>
   </si>
   <si>
-    <t>pct_classes_under_20</t>
-  </si>
-  <si>
-    <t>% of undergrad classes with fewer than 20 students</t>
-  </si>
-  <si>
-    <t>cds_ai</t>
-  </si>
-  <si>
-    <t>Academic Insights metric_id TBD</t>
-  </si>
-  <si>
-    <t>Percent of undergraduate class sections with fewer than 20 students enrolled. A staple of college rankings — high values usually indicate small-seminar-rich curricula. Common Data Set source (~45% coverage). Both this and pct_classes_50plus depend on how the institution counts sections.</t>
-  </si>
-  <si>
-    <t>pct_classes_50plus</t>
-  </si>
-  <si>
-    <t>% of undergrad classes with 50 or more students</t>
-  </si>
-  <si>
-    <t>Percent of undergraduate class sections with 50 or more students enrolled. Together with pct_classes_under_20, gives a coarse picture of class-size distribution. Common Data Set source — survey respondents only (~45%). Some institutions exclude labs/recitations differently.</t>
+    <t>Keep: ratio of instruction to total core expenses. Distinct from absolute spending.</t>
   </si>
   <si>
     <t>Finance</t>
@@ -196,9 +208,15 @@
     <t>(endowment_per_fte * FTE) / core_expenses</t>
   </si>
   <si>
+    <t>Higher = financially stronger. Most LACs 1-5; wealthiest research 10+</t>
+  </si>
+  <si>
     <t>Endowment value expressed as years of core operating expenses (endowment ÷ annual core expenses). A standard financial-strength measure: most LACs run 1–5 years of coverage; the wealthiest research universities can run 10+. Source: IPEDS F, derived.</t>
   </si>
   <si>
+    <t>Keep: distinct signal (endowment / annual operating expenses = years of cushion). Conceptually different from per-FTE wealth.</t>
+  </si>
+  <si>
     <t>tuition_share_of_expenses</t>
   </si>
   <si>
@@ -208,9 +226,15 @@
     <t>100 * (tuition_per_fte * FTE) / core_expenses</t>
   </si>
   <si>
+    <t>Stable analog of tuition_dependence; uses expenses (no investment-return distortion)</t>
+  </si>
+  <si>
     <t>Net tuition revenue as a percent of core operating expenses. A stable analog to tuition dependence — high values (&gt;80%) typify tuition-dependent schools; low values reflect heavy endowment or appropriations support. Uses expenses (not revenue) to avoid investment-return volatility. Source: IPEDS F, derived.</t>
   </si>
   <si>
+    <t>Keep: measures revenue-mix dependence on tuition. Distinct from absolute tuition or expenses.</t>
+  </si>
+  <si>
     <t>core_expenses_per_fte</t>
   </si>
   <si>
@@ -223,6 +247,9 @@
     <t>Total core operating expenses divided by full-time-equivalent enrollment. Core expenses include instruction, research, public service, academic support, student services, institutional support, O&amp;M, and depreciation. Excludes auxiliary services. Source: IPEDS Finance (F).</t>
   </si>
   <si>
+    <t>Keep? BUT, r = 0.871 with instruction_per_fte (Resources). Defensible because instruction is the largest single line item in core expenses; themes are conceptually separate.</t>
+  </si>
+  <si>
     <t>operating_margin_ex_inv_return_per_fte</t>
   </si>
   <si>
@@ -232,22 +259,13 @@
     <t>(rev * (1 - INVRPC/100) - core_exp) / FTE</t>
   </si>
   <si>
+    <t>Negative values common for endowment-rich schools that fund operations from endowment income</t>
+  </si>
+  <si>
     <t>Operating margin per FTE, excluding investment return. Operating revenue minus core expenses, normalized by enrollment. Negative values are common at endowment-heavy schools that fund operations from investment income — that's the point of excluding investment return here. Source: IPEDS F, derived.</t>
   </si>
   <si>
-    <t>net_assets_per_fte</t>
-  </si>
-  <si>
-    <t>Total net assets per FTE (year end)</t>
-  </si>
-  <si>
-    <t>F1A.F1H02 (FASB) / F2.F2H02 (GASB) / DRVEF.FTE</t>
-  </si>
-  <si>
-    <t>Total net assets at fiscal year-end, divided by FTE enrollment. Captures cumulative financial position (assets minus liabilities) per student. FASB and GASB reporters use different line items but they're combined here. Source: IPEDS F.</t>
-  </si>
-  <si>
-    <t>REMOVE — r = 0.998 with endowment_per_fte. Both measure institutional wealth; endowment_per_fte is the standard headline figure, net assets is the GAAP balance-sheet view. Keeping both creates a near-collinear bundle that destabilises Mahalanobis and adds no real signal under Euclidean.</t>
+    <t xml:space="preserve">Keep? Operational profitability with investment-return distortion stripped out. No high-correlation pair in the set. </t>
   </si>
   <si>
     <t>published_tuition_fees</t>
@@ -259,9 +277,15 @@
     <t>IC{yr}_AY.TUITION2 + FEE2 / COST1_2024.CHG2AY3</t>
   </si>
   <si>
+    <t>Combined tuition + fees. In-state used for public institutions.</t>
+  </si>
+  <si>
     <t>Published in-state undergraduate tuition plus required fees for the academic year. Sticker price, before any aid is considered. Use net price variables for what students actually pay. Source: IPEDS IC (TUITION2 + FEE2).</t>
   </si>
   <si>
+    <t>Keep? BUT,  r = 0.915 with avg_inst_grant (Aid theme). Cross-theme; reflects the classic high-sticker / big-discount pattern. Defensible to keep both.</t>
+  </si>
+  <si>
     <t>herd_avg</t>
   </si>
   <si>
@@ -274,62 +298,26 @@
     <t>Carnegie 2025 Public Data File.herd_avg</t>
   </si>
   <si>
+    <t>descriptive</t>
+  </si>
+  <si>
+    <t>NECHE peer-set member. One-time Carnegie snapshot (FY2020-2023 avg) under 2024.</t>
+  </si>
+  <si>
     <t>Three-year average of total R&amp;D expenditures from the NSF Higher Education Research and Development (HERD) survey, as reported in the Carnegie 2025 Public Data File. Headline indicator of research intensity. Excludes federally funded R&amp;D centers. One-time snapshot covering FY2020–2023.</t>
   </si>
   <si>
-    <t>Keep: No high-correlation pair within Resources or across themes.</t>
-  </si>
-  <si>
-    <t>Keep: distinct signal (% of instructional staff tenured/tenure-track). No correlation issues.</t>
-  </si>
-  <si>
-    <t>Keep? But r = 0.871 with core_expenses_per_fte (Finance). Cross-theme overlap is defensible. Drop only if consolidating finance and resources into one theme?</t>
-  </si>
-  <si>
-    <t>Keep: faculty-investment signal that's distinct from expenses-per-FTE.</t>
-  </si>
-  <si>
-    <t>Keep: distinct line item (libraries, IT support, academic administration).</t>
-  </si>
-  <si>
-    <t>Keep: distinct line item (advising, registrar, student-life support).</t>
-  </si>
-  <si>
-    <t>Keep: ratio of instruction to total core expenses. Distinct from absolute spending.</t>
-  </si>
-  <si>
-    <t>Keep: class-size discrimination signal (Liberal Arts Colleges vs research universities). No high-correlation pair.</t>
-  </si>
-  <si>
-    <t>Keep: large-class share, complements pct_classes_under_20. Distinct signal (some schools have neither, e.g., balanced mid-size schools).</t>
-  </si>
-  <si>
-    <t>Keep: anchor variable for institutional wealth. Pairs with endowment_coverage_years (a related ratio) as the canonical finance signal.</t>
-  </si>
-  <si>
-    <t>Keep: distinct signal (endowment / annual operating expenses = years of cushion). Conceptually different from per-FTE wealth.</t>
-  </si>
-  <si>
-    <t>Keep: measures revenue-mix dependence on tuition. Distinct from absolute tuition or expenses.</t>
-  </si>
-  <si>
-    <t>Keep? BUT, r = 0.871 with instruction_per_fte (Resources). Defensible because instruction is the largest single line item in core expenses; themes are conceptually separate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep? Operational profitability with investment-return distortion stripped out. No high-correlation pair in the set. </t>
-  </si>
-  <si>
-    <t>Keep? BUT,  r = 0.915 with avg_inst_grant (Aid theme). Cross-theme; reflects the classic high-sticker / big-discount pattern. Defensible to keep both.</t>
-  </si>
-  <si>
     <t>Keep? Research-expenditure signal. Distinct from all other finance vars.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep: anchor variable for institutional wealth. Pairs well with endowment_coverage_years (a related ratio). </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -342,20 +330,10 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,17 +343,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4EDEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -388,17 +355,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFAC9E94"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFAC9E94"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFAC9E94"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFAC9E94"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -406,22 +367,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,18 +671,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" customWidth="1"/>
-    <col min="2" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="8" width="80.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="60.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="70.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="50.6640625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,447 +712,438 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
